--- a/src/test/resources/testData/isa-open-valid.xlsx
+++ b/src/test/resources/testData/isa-open-valid.xlsx
@@ -203,7 +203,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
